--- a/data/trans_dic/IP19C07-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C07-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por ortodoncia</t>
+          <t>Menores que en su última visita al dentista fue por ortodoncia (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,87; 22,77</t>
+          <t>6,59; 22,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,65; 16,97</t>
+          <t>3,33; 16,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,03</t>
+          <t>0,0; 17,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,88</t>
+          <t>0,0; 15,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 12,44</t>
+          <t>1,45; 12,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 16,86</t>
+          <t>2,65; 18,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 17,36</t>
+          <t>1,95; 17,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,96; 14,72</t>
+          <t>5,0; 15,14</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,18; 13,41</t>
+          <t>3,7; 13,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 12,13</t>
+          <t>1,62; 12,89</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,82</t>
+          <t>0,0; 7,58</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,66; 14,09</t>
+          <t>7,75; 14,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,81; 10,71</t>
+          <t>4,81; 10,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,11; 10,37</t>
+          <t>4,93; 10,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,16; 9,75</t>
+          <t>4,17; 9,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,36; 13,76</t>
+          <t>7,27; 13,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,31; 11,64</t>
+          <t>5,27; 11,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 6,56</t>
+          <t>2,24; 6,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 8,17</t>
+          <t>3,56; 8,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,39; 12,75</t>
+          <t>8,27; 12,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,64; 9,73</t>
+          <t>5,77; 9,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,2; 7,59</t>
+          <t>4,02; 7,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,22; 7,87</t>
+          <t>4,27; 7,93</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,94; 25,46</t>
+          <t>9,78; 24,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,49; 24,58</t>
+          <t>10,92; 23,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,65; 19,8</t>
+          <t>7,05; 19,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,51; 18,93</t>
+          <t>7,43; 18,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,9; 20,08</t>
+          <t>7,19; 21,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,37; 24,64</t>
+          <t>11,37; 24,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,09; 16,58</t>
+          <t>5,8; 17,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,15; 11,89</t>
+          <t>4,38; 11,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,47; 19,62</t>
+          <t>10,14; 19,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,56; 22,43</t>
+          <t>12,57; 22,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,57; 15,82</t>
+          <t>7,61; 16,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,32; 13,41</t>
+          <t>6,59; 13,13</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,37; 15,09</t>
+          <t>9,47; 15,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,43; 12,55</t>
+          <t>7,26; 12,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,96; 11,05</t>
+          <t>5,88; 11,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,62; 10,53</t>
+          <t>5,92; 10,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,67; 12,91</t>
+          <t>7,5; 12,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,56; 12,71</t>
+          <t>7,66; 12,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,05</t>
+          <t>4,04; 7,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,86</t>
+          <t>4,0; 8,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,16; 13,06</t>
+          <t>9,32; 13,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,1; 11,88</t>
+          <t>8,05; 11,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,55; 8,62</t>
+          <t>5,43; 8,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,14; 8,24</t>
+          <t>5,21; 8,17</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por ortodoncia (tasa de respuesta: 99,51%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>6095</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3957</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3107</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1777</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>8057</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7064</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2613</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3092; 10528</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1596; 8114</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3922</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4696</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>622; 5235</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1138; 7807</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>549; 4883</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>4488; 13602</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3364; 12421</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>813; 6479</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4185</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>24392</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16194</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18536</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>16737</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>25062</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>18858</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>9788</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>17737</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>49453</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>35052</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>28324</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>34474</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>17694; 33125</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>10607; 23243</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>12470; 26736</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>10920; 24310</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>17859; 33295</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>12693; 26548</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>5648; 16611</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>11498; 27630</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>39206; 60096</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>26635; 45205</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>20278; 38219</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>24982; 46402</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>12411</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14186</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10320</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>12311</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>14188</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>9331</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>10143</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>21615</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>28374</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>19651</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>22454</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>7405; 18436</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9426; 20378</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6244; 17594</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7434; 18848</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5257; 15357</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>9341; 20510</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5090; 14975</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>5956; 15948</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>15094; 29220</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>21162; 37272</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>13415; 28605</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>15556; 30978</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>42898</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>34337</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>29692</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>30358</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>36227</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>36153</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>20895</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>27880</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>79125</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>70490</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>50587</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>58238</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>33248; 53716</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>25757; 43994</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>21373; 39972</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>23186; 41294</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>27139; 45993</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>28052; 47275</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>14857; 29276</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>19399; 38966</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>66442; 94353</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>58006; 85017</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>39744; 62906</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>45682; 71610</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C07-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C07-Estudios-trans_dic.xlsx
@@ -717,37 +717,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,59; 22,44</t>
+          <t>5,97; 22,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,33; 16,92</t>
+          <t>3,39; 16,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,72</t>
+          <t>0,0; 17,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,8</t>
+          <t>0,0; 14,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 12,21</t>
+          <t>1,47; 12,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 18,17</t>
+          <t>1,53; 17,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 17,35</t>
+          <t>1,9; 16,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,0; 15,14</t>
+          <t>5,03; 14,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 13,66</t>
+          <t>3,97; 13,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 12,89</t>
+          <t>1,23; 12,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,58</t>
+          <t>0,0; 7,83</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,75; 14,51</t>
+          <t>7,71; 14,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,81; 10,54</t>
+          <t>4,86; 10,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,93; 10,58</t>
+          <t>4,95; 10,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,17; 9,28</t>
+          <t>4,04; 9,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,27; 13,55</t>
+          <t>7,5; 13,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,27; 11,02</t>
+          <t>5,31; 11,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 6,59</t>
+          <t>2,27; 6,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,56; 8,55</t>
+          <t>3,53; 8,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,27; 12,68</t>
+          <t>8,37; 13,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,77; 9,8</t>
+          <t>5,7; 10,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,02; 7,57</t>
+          <t>4,09; 7,71</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 7,93</t>
+          <t>4,28; 7,9</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,78; 24,36</t>
+          <t>10,0; 24,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,92; 23,62</t>
+          <t>10,29; 22,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,05; 19,88</t>
+          <t>6,81; 18,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,43; 18,83</t>
+          <t>7,49; 19,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,19; 21,0</t>
+          <t>7,44; 20,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,37; 24,97</t>
+          <t>11,45; 25,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,8; 17,08</t>
+          <t>5,88; 16,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,38; 11,73</t>
+          <t>4,41; 12,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,14; 19,64</t>
+          <t>10,35; 19,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,57; 22,13</t>
+          <t>12,74; 21,87</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,61; 16,23</t>
+          <t>7,34; 15,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,59; 13,13</t>
+          <t>6,66; 13,21</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,47; 15,31</t>
+          <t>9,73; 15,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,26; 12,4</t>
+          <t>7,29; 12,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,88; 11,0</t>
+          <t>5,93; 11,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,92; 10,54</t>
+          <t>5,64; 10,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,5; 12,71</t>
+          <t>7,79; 12,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,66; 12,92</t>
+          <t>7,58; 12,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,96</t>
+          <t>3,94; 7,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,0; 8,04</t>
+          <t>4,12; 7,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,32; 13,24</t>
+          <t>9,35; 13,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,05; 11,8</t>
+          <t>8,09; 11,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,43; 8,6</t>
+          <t>5,57; 8,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,21; 8,17</t>
+          <t>5,23; 8,22</t>
         </is>
       </c>
     </row>
@@ -1504,37 +1504,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3092; 10528</t>
+          <t>2800; 10388</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1596; 8114</t>
+          <t>1628; 8111</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3922</t>
+          <t>0; 3808</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4696</t>
+          <t>0; 4316</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>622; 5235</t>
+          <t>633; 5335</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1138; 7807</t>
+          <t>657; 7709</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>549; 4883</t>
+          <t>533; 4775</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1544,22 +1544,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4488; 13602</t>
+          <t>4513; 13027</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3364; 12421</t>
+          <t>3609; 12421</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>813; 6479</t>
+          <t>619; 6462</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 4185</t>
+          <t>0; 4324</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17694; 33125</t>
+          <t>17594; 32619</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10607; 23243</t>
+          <t>10719; 22846</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12470; 26736</t>
+          <t>12504; 26375</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10920; 24310</t>
+          <t>10589; 24961</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17859; 33295</t>
+          <t>18418; 33994</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12693; 26548</t>
+          <t>12781; 26907</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5648; 16611</t>
+          <t>5722; 15813</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11498; 27630</t>
+          <t>11390; 27475</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39206; 60096</t>
+          <t>39684; 62320</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26635; 45205</t>
+          <t>26309; 46408</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20278; 38219</t>
+          <t>20674; 38915</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24982; 46402</t>
+          <t>25037; 46201</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7405; 18436</t>
+          <t>7568; 18632</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9426; 20378</t>
+          <t>8880; 19686</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6244; 17594</t>
+          <t>6025; 16671</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7434; 18848</t>
+          <t>7497; 19914</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5257; 15357</t>
+          <t>5438; 14735</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9341; 20510</t>
+          <t>9401; 20930</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5090; 14975</t>
+          <t>5154; 14587</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5956; 15948</t>
+          <t>6001; 16567</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15094; 29220</t>
+          <t>15397; 29430</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21162; 37272</t>
+          <t>21451; 36825</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13415; 28605</t>
+          <t>12939; 27889</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15556; 30978</t>
+          <t>15715; 31175</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33248; 53716</t>
+          <t>34135; 53121</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25757; 43994</t>
+          <t>25853; 43860</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21373; 39972</t>
+          <t>21548; 39995</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23186; 41294</t>
+          <t>22072; 41057</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27139; 45993</t>
+          <t>28173; 46308</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28052; 47275</t>
+          <t>27746; 46738</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14857; 29276</t>
+          <t>14488; 28954</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19399; 38966</t>
+          <t>19975; 38241</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>66442; 94353</t>
+          <t>66619; 94096</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>58006; 85017</t>
+          <t>58317; 84678</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39744; 62906</t>
+          <t>40738; 63133</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45682; 71610</t>
+          <t>45816; 72029</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C07-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C07-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,57%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6,31%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>12,99%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>8,25%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3,78%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,41%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,31%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,97; 22,14</t>
+          <t>1,48; 12,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,39; 16,91</t>
+          <t>2,65; 16,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,2</t>
+          <t>1,93; 17,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 12,44</t>
+          <t>6,87; 22,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 17,94</t>
+          <t>3,65; 16,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 16,97</t>
+          <t>0,0; 15,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 13,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,03; 14,5</t>
+          <t>4,96; 14,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,97; 13,66</t>
+          <t>4,18; 13,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 12,85</t>
+          <t>1,64; 12,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,83</t>
+          <t>0,0; 8,16</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10,2%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7,83%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3,88%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5,73%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>10,68%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>7,35%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>7,33%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,39%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,83%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,71; 14,29</t>
+          <t>7,36; 13,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,86; 10,36</t>
+          <t>5,31; 11,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,95; 10,44</t>
+          <t>2,17; 6,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,04; 9,53</t>
+          <t>3,42; 8,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,5; 13,83</t>
+          <t>7,66; 14,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,31; 11,17</t>
+          <t>4,81; 10,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,27</t>
+          <t>5,11; 10,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 8,51</t>
+          <t>4,29; 10,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,37; 13,15</t>
+          <t>8,39; 12,75</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,7; 10,06</t>
+          <t>5,64; 9,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 7,71</t>
+          <t>4,2; 7,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,28; 7,9</t>
+          <t>4,36; 8,17</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>12,59%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17,28%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10,64%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7,99%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>16,4%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>16,44%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>11,66%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12,3%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>12,59%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>17,28%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10,64%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,0; 24,62</t>
+          <t>6,9; 20,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,29; 22,82</t>
+          <t>11,37; 24,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,81; 18,83</t>
+          <t>6,09; 16,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,49; 19,9</t>
+          <t>4,4; 12,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,44; 20,15</t>
+          <t>10,94; 25,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,45; 25,49</t>
+          <t>10,49; 24,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,88; 16,63</t>
+          <t>6,65; 19,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,41; 12,19</t>
+          <t>7,47; 18,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,35; 19,78</t>
+          <t>10,47; 19,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,74; 21,87</t>
+          <t>12,56; 22,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,34; 15,83</t>
+          <t>7,57; 15,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,66; 13,21</t>
+          <t>6,66; 14,19</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,88%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,68%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6,05%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>12,22%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9,68%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>8,17%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,88%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,73; 15,14</t>
+          <t>7,67; 12,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 12,36</t>
+          <t>7,56; 12,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,93; 11,01</t>
+          <t>4,08; 8,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,64; 10,48</t>
+          <t>4,29; 8,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,79; 12,8</t>
+          <t>9,37; 15,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,58; 12,77</t>
+          <t>7,43; 12,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,94; 7,87</t>
+          <t>5,96; 11,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,12; 7,89</t>
+          <t>5,77; 10,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,35; 13,2</t>
+          <t>9,16; 13,06</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,09; 11,75</t>
+          <t>8,1; 11,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,57; 8,63</t>
+          <t>5,55; 8,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 8,22</t>
+          <t>5,31; 8,52</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3107</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1777</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>6095</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>3957</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>836</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1310</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3107</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1777</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1265</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2800; 10388</t>
+          <t>633; 5337</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1628; 8111</t>
+          <t>1141; 7243</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3808</t>
+          <t>542; 4885</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4316</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>633; 5335</t>
+          <t>3226; 10687</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>657; 7709</t>
+          <t>1750; 8141</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>533; 4775</t>
+          <t>0; 3328</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3592</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4513; 13027</t>
+          <t>4454; 13223</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3609; 12421</t>
+          <t>3799; 12194</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>619; 6462</t>
+          <t>827; 6101</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 4324</t>
+          <t>0; 4156</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>25062</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18858</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9788</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17751</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>24392</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>16194</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>18536</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>16737</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>25062</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18858</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9788</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17737</t>
+          <t>17549</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>34474</t>
+          <t>35300</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17594; 32619</t>
+          <t>18077; 33809</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10719; 22846</t>
+          <t>12793; 28035</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12504; 26375</t>
+          <t>5483; 16544</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10589; 24961</t>
+          <t>10572; 26154</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18418; 33994</t>
+          <t>17496; 32179</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12781; 26907</t>
+          <t>10600; 23624</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5722; 15813</t>
+          <t>12921; 26216</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11390; 27475</t>
+          <t>11403; 27345</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39684; 62320</t>
+          <t>39783; 60421</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26309; 46408</t>
+          <t>26016; 44892</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20674; 38915</t>
+          <t>21194; 38341</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25037; 46201</t>
+          <t>25090; 47014</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14188</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9331</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10163</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>12411</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>14186</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>10320</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>12311</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>9203</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>14188</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9331</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>12655</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22454</t>
+          <t>22817</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7568; 18632</t>
+          <t>5043; 14685</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8880; 19686</t>
+          <t>9339; 20233</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6025; 16671</t>
+          <t>5337; 14545</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7497; 19914</t>
+          <t>5599; 16255</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5438; 14735</t>
+          <t>8277; 19266</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9401; 20930</t>
+          <t>9048; 21212</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5154; 14587</t>
+          <t>5885; 17530</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6001; 16567</t>
+          <t>7740; 19658</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15397; 29430</t>
+          <t>15583; 29201</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21451; 36825</t>
+          <t>21157; 37771</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12939; 27889</t>
+          <t>13336; 27869</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15715; 31175</t>
+          <t>15366; 32755</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>40</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>36227</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>36153</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20895</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>27914</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>42898</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>34337</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>29692</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>30358</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>36227</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>36153</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>20895</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>27880</t>
+          <t>31469</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>58238</t>
+          <t>59383</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34135; 53121</t>
+          <t>27746; 46699</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25853; 43860</t>
+          <t>27652; 46512</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21548; 39995</t>
+          <t>15014; 29636</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22072; 41057</t>
+          <t>19800; 38307</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28173; 46308</t>
+          <t>32872; 52969</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27746; 46738</t>
+          <t>26370; 44516</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14488; 28954</t>
+          <t>21653; 40170</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19975; 38241</t>
+          <t>22847; 42910</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>66619; 94096</t>
+          <t>65315; 93057</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>58317; 84678</t>
+          <t>58351; 85608</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40738; 63133</t>
+          <t>40567; 63057</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45816; 72029</t>
+          <t>45499; 73060</t>
         </is>
       </c>
     </row>
